--- a/output/laminas_provinciales/prov_i_ingr_median_a_2023_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2023_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:12</t>
+    <t xml:space="preserve">2026-09-09 22:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2023_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2023_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:09</t>
+    <t xml:space="preserve">2026-09-17 13:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,18 +955,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>829520</v>
+        <v>840290</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>840290</v>
+        <v>829520</v>
       </c>
     </row>
     <row r="4">
@@ -1015,68 +1015,68 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>721470</v>
+        <v>749901</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>829520</v>
+        <v>840290</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>875000</v>
+        <v>885081.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>749901</v>
+        <v>721470</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>840290</v>
+        <v>829520</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>885081.5</v>
+        <v>875000</v>
       </c>
     </row>
     <row r="8">

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2023_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2023_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:38</t>
+    <t xml:space="preserve">2026-09-25 21:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_median_a_2023_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_median_a_2023_los_lagos.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:38</t>
+    <t xml:space="preserve">2026-10-05 07:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -488,7 +488,7 @@
         <v>817903</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>721532</v>
+        <v>721533</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="n">
